--- a/TouhouSurvival/Assets/StreamingAssets/AttributeTables/PlayableCharacters/moscow.xlsx
+++ b/TouhouSurvival/Assets/StreamingAssets/AttributeTables/PlayableCharacters/moscow.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\PlayableCharacters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E24BDB-9E0C-46A0-A2EA-D5B914F35509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD42A749-7196-4012-A6D2-49DD4CA8F7E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="540" yWindow="2790" windowWidth="19395" windowHeight="12360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="38">
   <si>
     <t>Attribute Type</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -157,6 +157,10 @@
   </si>
   <si>
     <t>이동속도 0.05 증가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HealthRegeneration</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -480,7 +484,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="24.625" customWidth="1"/>
@@ -653,6 +657,14 @@
       </c>
       <c r="B18">
         <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>

--- a/TouhouSurvival/Assets/StreamingAssets/AttributeTables/PlayableCharacters/moscow.xlsx
+++ b/TouhouSurvival/Assets/StreamingAssets/AttributeTables/PlayableCharacters/moscow.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\PlayableCharacters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD42A749-7196-4012-A6D2-49DD4CA8F7E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13D7A492-646B-4C5E-BF17-5C8FA7361A86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7545" yWindow="2115" windowWidth="19395" windowHeight="12360" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base" sheetId="1" r:id="rId1"/>
@@ -31,58 +31,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Health</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MovementSpeed</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HealthRecovery</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Defense</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ScanRangeMultiplier</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ExpGainIncrease</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CooldownDecrease</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackStrength</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ProjectileSpeedChange</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ProjectileSizeChange</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ProjectileDurationChange</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ProjectileIncreaseCount</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Lucky</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -160,7 +108,59 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>HealthRegeneration</t>
+    <t>HpMax</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRegen</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Speed</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PickRange</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExpGain</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cooldown</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Knockback</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjSpeed</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjSize</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjLifetime</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjCount</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpellCardGaugeAcquisitionRateChange</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -487,7 +487,8 @@
   <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="24.625" customWidth="1"/>
+    <col min="1" max="1" width="48.625" customWidth="1"/>
+    <col min="2" max="2" width="24.625" customWidth="1"/>
     <col min="3" max="11" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -502,7 +503,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="B2">
         <v>10</v>
@@ -514,10 +515,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>0.01</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -526,10 +527,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4">
         <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -538,15 +539,15 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -554,7 +555,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -562,7 +563,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -570,15 +571,15 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -586,7 +587,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -598,7 +599,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -609,7 +610,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -621,7 +622,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -629,7 +630,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -637,34 +638,34 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B17">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="B19">
-        <v>0.01</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -685,19 +686,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -705,16 +706,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C2">
         <v>0.05</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -722,16 +723,16 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C3">
         <v>0.01</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -739,16 +740,16 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C4">
         <v>0.01</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -756,16 +757,16 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C5">
         <v>0.01</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -773,16 +774,16 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C6">
         <v>0.01</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -790,16 +791,16 @@
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C7">
         <v>0.01</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -807,16 +808,16 @@
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C8">
         <v>0.01</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -824,16 +825,16 @@
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C9">
         <v>0.01</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -841,16 +842,16 @@
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C10">
         <v>0.01</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -858,16 +859,16 @@
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C11">
         <v>0.01</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -875,16 +876,16 @@
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C12">
         <v>0.01</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -892,16 +893,16 @@
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C13">
         <v>0.01</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -909,16 +910,16 @@
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C14">
         <v>0.01</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -926,16 +927,16 @@
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C15">
         <v>0.01</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -943,16 +944,16 @@
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C16">
         <v>0.01</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -960,16 +961,16 @@
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C17">
         <v>0.01</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -977,16 +978,16 @@
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>0.01</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -994,16 +995,16 @@
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C19">
         <v>0.01</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1011,16 +1012,16 @@
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C20">
         <v>0.01</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -1028,16 +1029,16 @@
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C21">
         <v>0.01</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1045,16 +1046,16 @@
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C22">
         <v>0.01</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1062,16 +1063,16 @@
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C23">
         <v>0.01</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1079,16 +1080,16 @@
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C24">
         <v>0.01</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1096,16 +1097,16 @@
         <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C25">
         <v>0.01</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -1113,16 +1114,16 @@
         <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C26">
         <v>0.01</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -1130,16 +1131,16 @@
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C27">
         <v>0.01</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -1147,16 +1148,16 @@
         <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C28">
         <v>0.01</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -1164,16 +1165,16 @@
         <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C29">
         <v>0.01</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -1181,16 +1182,16 @@
         <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C30">
         <v>1.01</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -1198,16 +1199,16 @@
         <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C31">
         <v>2.0099999999999998</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -1215,16 +1216,16 @@
         <v>32</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C32">
         <v>3.01</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1232,16 +1233,16 @@
         <v>33</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C33">
         <v>4.01</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -1249,16 +1250,16 @@
         <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C34">
         <v>5.01</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -1266,16 +1267,16 @@
         <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C35">
         <v>6.01</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -1283,16 +1284,16 @@
         <v>36</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C36">
         <v>7.01</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -1300,16 +1301,16 @@
         <v>37</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C37">
         <v>8.01</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -1317,16 +1318,16 @@
         <v>38</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C38">
         <v>9.01</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -1334,16 +1335,16 @@
         <v>39</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C39">
         <v>10.01</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -1351,16 +1352,16 @@
         <v>40</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C40">
         <v>11.01</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/TouhouSurvival/Assets/StreamingAssets/AttributeTables/PlayableCharacters/moscow.xlsx
+++ b/TouhouSurvival/Assets/StreamingAssets/AttributeTables/PlayableCharacters/moscow.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\PlayableCharacters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\PlayableCharacters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD42A749-7196-4012-A6D2-49DD4CA8F7E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D2783A-4074-4C84-9A27-C1310B52A7EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2565" yWindow="9090" windowWidth="28800" windowHeight="17145" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="38">
   <si>
     <t>Attribute Type</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -31,58 +31,14 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Health</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>MovementSpeed</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>HealthRecovery</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Defense</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>ScanRangeMultiplier</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ExpGainIncrease</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CooldownDecrease</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackStrength</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ProjectileSpeedChange</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ProjectileSizeChange</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ProjectileDurationChange</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ProjectileIncreaseCount</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Lucky</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -160,7 +116,51 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>HealthRegeneration</t>
+    <t>HpMax</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Speed</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRegen</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PickRange</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExpGain</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cooldown</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjSpeed</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjSize</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjLifetime</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjCount</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -484,7 +484,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="24.625" customWidth="1"/>
@@ -502,7 +502,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="B2">
         <v>10</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -526,7 +526,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -538,15 +538,15 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -554,15 +554,15 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -578,50 +578,50 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
       <c r="F11" s="1"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
       <c r="F12" s="1"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -629,41 +629,33 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B17">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B18">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19">
         <v>0.01</v>
       </c>
     </row>
@@ -685,19 +677,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -705,16 +697,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2">
         <v>0.05</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -722,16 +714,16 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3">
         <v>0.01</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -739,16 +731,16 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C4">
         <v>0.01</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -756,16 +748,16 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5">
         <v>0.01</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -773,16 +765,16 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6">
         <v>0.01</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -790,16 +782,16 @@
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C7">
         <v>0.01</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -807,16 +799,16 @@
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8">
         <v>0.01</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -824,16 +816,16 @@
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C9">
         <v>0.01</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -841,16 +833,16 @@
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10">
         <v>0.01</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -858,16 +850,16 @@
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C11">
         <v>0.01</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -875,16 +867,16 @@
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12">
         <v>0.01</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -892,16 +884,16 @@
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C13">
         <v>0.01</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -909,16 +901,16 @@
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C14">
         <v>0.01</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -926,16 +918,16 @@
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15">
         <v>0.01</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -943,16 +935,16 @@
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C16">
         <v>0.01</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -960,16 +952,16 @@
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C17">
         <v>0.01</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -977,16 +969,16 @@
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C18">
         <v>0.01</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -994,16 +986,16 @@
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C19">
         <v>0.01</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1011,16 +1003,16 @@
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C20">
         <v>0.01</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -1028,16 +1020,16 @@
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C21">
         <v>0.01</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1045,16 +1037,16 @@
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C22">
         <v>0.01</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1062,16 +1054,16 @@
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C23">
         <v>0.01</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1079,16 +1071,16 @@
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C24">
         <v>0.01</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1096,16 +1088,16 @@
         <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C25">
         <v>0.01</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -1113,16 +1105,16 @@
         <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C26">
         <v>0.01</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -1130,16 +1122,16 @@
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C27">
         <v>0.01</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -1147,16 +1139,16 @@
         <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C28">
         <v>0.01</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -1164,16 +1156,16 @@
         <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C29">
         <v>0.01</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -1181,16 +1173,16 @@
         <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C30">
         <v>1.01</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -1198,16 +1190,16 @@
         <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C31">
         <v>2.0099999999999998</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -1215,16 +1207,16 @@
         <v>32</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C32">
         <v>3.01</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1232,16 +1224,16 @@
         <v>33</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C33">
         <v>4.01</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -1249,16 +1241,16 @@
         <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C34">
         <v>5.01</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -1266,16 +1258,16 @@
         <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C35">
         <v>6.01</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -1283,16 +1275,16 @@
         <v>36</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C36">
         <v>7.01</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -1300,16 +1292,16 @@
         <v>37</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C37">
         <v>8.01</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -1317,16 +1309,16 @@
         <v>38</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C38">
         <v>9.01</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -1334,16 +1326,16 @@
         <v>39</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C39">
         <v>10.01</v>
       </c>
       <c r="D39" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -1351,16 +1343,16 @@
         <v>40</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C40">
         <v>11.01</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
